--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8DA1B2-66DF-4337-89C5-6F410983A980}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="177">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -57,13 +57,7 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>[e.g., ~150]</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
-  </si>
-  <si>
-    <t>[e.g., 18]</t>
   </si>
   <si>
     <t>Selection Ratio:</t>
@@ -1300,22 +1294,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1327,6 +1305,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1641,14 +1635,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
@@ -1657,10 +1651,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1668,7 +1662,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.8" customHeight="1">
@@ -1676,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.2" customHeight="1">
@@ -1684,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
@@ -1696,102 +1690,102 @@
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
+      <c r="C10">
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C11" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="e">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>#VALUE!</v>
+        <v>9.166666666666666E-2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1799,62 +1793,62 @@
     </row>
     <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1882,313 +1876,313 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="A1" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:13" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="100.05" customHeight="1">
       <c r="A4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="100.05" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="100.05" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="117.6" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="24" t="s">
+      <c r="B7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="F7" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="G7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="H7" s="19" t="s">
         <v>144</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="79.95" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="F8" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="G8" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="H8" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="79.95" customHeight="1">
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="B9" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="F9" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="G9" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="H9" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:13" ht="79.95" customHeight="1">
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="E10" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="F10" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="G10" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="H10" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
     </row>
     <row r="11" spans="1:13" ht="126.6" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="E11" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="F11" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="G11" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="H11" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:13" ht="79.95" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="F12" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="G12" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="H12" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
     </row>
     <row r="13" spans="1:13" ht="79.95" customHeight="1">
       <c r="A13" s="7"/>
@@ -2199,11 +2193,11 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
     </row>
     <row r="14" spans="1:13" ht="79.95" customHeight="1">
       <c r="A14" s="7"/>
@@ -2355,68 +2349,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2578,73 +2572,73 @@
     </row>
     <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2668,221 +2662,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="D13" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2890,7 +2884,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2898,7 +2892,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8DA1B2-66DF-4337-89C5-6F410983A980}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3374332D-ECBA-4F4E-8861-FF3858CC58A2}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="198">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1105,6 +1105,309 @@
   </si>
   <si>
     <t>Bản render SVG Final vuông vức hoàn hảo.</t>
+  </si>
+  <si>
+    <t>Repository / File I/O</t>
+  </si>
+  <si>
+    <t>Phải viết code đọc/ghi CSV cho 7 Entity khác nhau. Cần giải pháp tránh lặp code (Duplicate code).</t>
+  </si>
+  <si>
+    <t>"Viết class CsvRepository dùng Generics trong Java để đọc ghi file CSV cho tất cả các Entity tự động bằng Reflection."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI cung cấp class dùng thư viện </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>java.lang.reflect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để tự động map các cột CSV vào các thuộc tính (fields) của Object.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận thấy dùng Reflection liên tục khi đọc/ghi 10.000 dòng dữ liệu sẽ làm giảm hiệu năng hệ thống cực kỳ nghiêm trọng (Bottleneck).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Dự án yêu cầu đo lường TPS khắt khe nên tốc độ File I/O là cốt lõi.
+Creative Synthesis: Hủy bỏ Reflection. Chuyển sang ép kiểu thông qua 2 hàm abstract toCsvLine() và fromCsvLine() ở BaseEntity.
+Decision: Tối ưu hóa tốc độ parse CSV bằng việc xử lý chuỗi thủ công trong từng model.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Source code abstract class </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CsvRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BaseEntity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Omission / Context Loss</t>
+  </si>
+  <si>
+    <t>Sơ đồ Class Diagram đã vẽ đầy đủ cấu trúc MVC của project.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sơ đồ bị khuyết hoàn toàn package </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>model</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (chứa các Entity lõi) do ảnh chụp đầu vào bị cắt mép.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đối chiếu sơ đồ AI sinh ra với cấu trúc thư mục thực tế trên IDE.</t>
+  </si>
+  <si>
+    <t>Bổ sung hình chụp góc bị khuất và yêu cầu AI merge lại thành bản kiến trúc đầy đủ.</t>
+  </si>
+  <si>
+    <t>Logic Flaw / Unoptimized Code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đoạn code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DataGenerator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có thể sinh 10,000 dòng CSV an toàn bằng cách nạp hết vào </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>List&lt;T&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đẩy 10,000+ object lên RAM cùng lúc gây nguy cơ tràn bộ nhớ (OutOfMemoryError) trên máy cấu hình thấp.</t>
+  </si>
+  <si>
+    <t>Review logic lưu trữ và đánh giá Big O (Space Complexity).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xóa logic của AI. Tự viết lại cơ chế Batch Processing (chia lô), cứ 500 object thì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>flush()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> xuống ổ cứng 1 lần.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logic Flaw / Infinite Loop</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cơ chế </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Optimistic Lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tự động retry 3 lần thành công khi bị lệch version.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vòng lặp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bị lỗi vô hạn (Infinite Loop) do AI quên lệnh gọi đọc lại data (fetch new version) từ file CSV.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chạy debug / Test tay thấy thread bị treo cứng khi có tranh chấp (Race Condition).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sửa tay đưa hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>findById()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào ngay dòng đầu tiên bên trong vòng lặp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để cập nhật version mới nhất.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1114,7 +1417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1203,6 +1506,11 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1230,7 +1538,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1253,11 +1561,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1306,12 +1625,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1319,8 +1644,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1337,6 +1662,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1635,14 +1964,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
@@ -1876,28 +2205,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -2184,15 +2513,31 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
     </row>
-    <row r="13" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+    <row r="13" spans="1:13" ht="151.80000000000001" customHeight="1">
+      <c r="A13" s="29">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>182</v>
+      </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
@@ -2349,24 +2694,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -2388,7 +2733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1">
+    <row r="4" spans="1:6" ht="35.4" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>62</v>
       </c>
@@ -2408,31 +2753,61 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+    <row r="5" spans="1:6" ht="92.4" customHeight="1">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="B6" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="B7" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="7"/>
@@ -2662,20 +3037,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
@@ -2703,7 +3078,7 @@
       <c r="B6" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="22" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="13"/>
@@ -2715,7 +3090,7 @@
       <c r="B7" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="22" t="s">
         <v>110</v>
       </c>
       <c r="D7" s="13"/>

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3374332D-ECBA-4F4E-8861-FF3858CC58A2}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC47191-6C60-4379-B382-A35143093859}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="200">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -183,76 +183,16 @@
     <t>001</t>
   </si>
   <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
     <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -1407,6 +1347,367 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> để cập nhật version mới nhất.</t>
+    </r>
+  </si>
+  <si>
+    <t>CODE GENERATION</t>
+  </si>
+  <si>
+    <t>Data Generator Tool</t>
+  </si>
+  <si>
+    <t>Đề bài yêu cầu tạo file CSV mồi có ≥ 10.000 dòng. Cần sinh dữ liệu giả (Mock data) nhưng không làm treo máy.</t>
+  </si>
+  <si>
+    <t>"Viết hàm DataGenerator sinh 5000 Products và 2000 Customers lưu ra file CSV."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI viết vòng lặp tạo toàn bộ object ném vào một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>List&lt;T&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khổng lồ, sau đó mới dùng stream ghi ra file CSV cùng một lúc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận thấy thuật toán của AI lưu 10.000+ object trên RAM cùng lúc dễ gây tràn bộ nhớ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>OutOfMemoryError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) trên máy cấu hình thấp.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Creative Synthesis: Hủy cách làm của AI, tự thiết kế lại thành kỹ thuật Batch Processing (Chia lô). Cứ tạo 500 dòng là flush() xuống ổ cứng và làm sạch list.
+Decision: Chốt phương án sinh dữ liệu theo lô để tối ưu RAM.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Code vòng lặp sinh dữ liệu trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DataGenerator.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Concurrency / FILE_LOCK</t>
+  </si>
+  <si>
+    <t>Cần khóa file cấp độ hệ điều hành (OS-level lock) để tránh đa luồng ghi đè file CSV cùng lúc gây hỏng dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Làm sao dùng FileChannel trong Java nio để khóa file flash_items.csv an toàn khi có đa luồng?"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI gợi ý gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FileChannel.open()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và dùng lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>channel.lock()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để block các luồng khác không cho phép ghi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sellWithFileLock()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chứa khối </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>try-finally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chặt chẽ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phát hiện code AI thiếu cơ chế giải phóng tài nguyên. Nếu luồng đang ghi bị văng Exception, file sẽ bị khóa vĩnh viễn (Deadlock).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Xử lý đa luồng bắt buộc phải dọn dẹp tài nguyên (cleanup) cẩn thận.
+Decision: Bắt buộc bọc lệnh lock() trong khối try và gọi lock.release() ở khối finally.</t>
+    </r>
+  </si>
+  <si>
+    <t>Concurrency / SYNCHRONIZED</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cài đặt cơ chế JVM Lock, nhưng khi gắn từ khóa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>synchronized</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào phương thức </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sell()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, thông lượng (TPS) giảm đến 80%.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Tại sao dùng phương thức synchronized lại làm rớt TPS nghiêm trọng? Có cách nào tối ưu hơn không?"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI giải thích do khóa cả phương thức (Method-level lock), khiến luồng mua sản phẩm A cũng phải chờ luồng mua sản phẩm B. Gợi ý đổi sang Block-level lock: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>synchronized(productId.intern())</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khối mã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>synchronized(itemId.intern())</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong Repository.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hiểu được sự tắc nghẽn (bottleneck) của khóa toàn cục. Thuật toán dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>intern()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của AI rất thông minh vì nó chia sẻ chung String pool cho các ID sản phẩm giống nhau.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Decision: Áp dụng khóa theo block ID sản phẩm, tốc độ TPS lập tức tăng vọt gấp 3 lần.</t>
     </r>
   </si>
 </sst>
@@ -1628,24 +1929,24 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1964,14 +2265,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
@@ -1980,10 +2281,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1991,7 +2292,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.8" customHeight="1">
@@ -1999,7 +2300,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.2" customHeight="1">
@@ -2007,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
@@ -2205,28 +2506,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:13" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -2255,133 +2556,129 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="C4" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="100.05" customHeight="1">
+      <c r="A5" s="7"/>
+      <c r="B5" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>61</v>
+      <c r="C5" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>69</v>
+      <c r="A6" s="7"/>
+      <c r="B6" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="117.6" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>139</v>
+      <c r="B7" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>141</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="79.95" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>145</v>
+      <c r="B8" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>148</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -2393,26 +2690,26 @@
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>151</v>
+      <c r="B9" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>154</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -2424,26 +2721,26 @@
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>158</v>
+      <c r="B10" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>160</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -2451,98 +2748,83 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:13" ht="126.6" customHeight="1">
+    <row r="11" spans="1:13" s="19" customFormat="1" ht="126.6" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-    </row>
-    <row r="12" spans="1:13" ht="79.95" customHeight="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" ht="151.80000000000001" customHeight="1">
-      <c r="A13" s="29">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="19" customFormat="1" ht="151.80000000000001" customHeight="1">
+      <c r="A13" s="23">
         <v>10</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>177</v>
+      <c r="B13" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>194</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
+        <v>198</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="79.95" customHeight="1">
       <c r="A14" s="7"/>
@@ -2694,63 +2976,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="A1" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+      <c r="A2" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="35.4" customHeight="1">
       <c r="A4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="92.4" customHeight="1">
@@ -2758,55 +3040,55 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="19" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="19" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
@@ -2947,73 +3229,73 @@
     </row>
     <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="7" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3037,202 +3319,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="A1" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="A2" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
@@ -3240,13 +3522,13 @@
         <v>40</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3259,7 +3541,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -3267,7 +3549,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC47191-6C60-4379-B382-A35143093859}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63F3C75-B2C4-4CD6-9B22-ED7D6C095E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="191">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -222,18 +222,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -400,341 +388,6 @@
   </si>
   <si>
     <t>E-Commerce Flash Sale Simulation</t>
-  </si>
-  <si>
-    <t>Architecture Design (MVC Decomposition)</t>
-  </si>
-  <si>
-    <t>Cần chuyển đổi tài liệu đặc tả (Word) thành sơ đồ lớp chuẩn cấu trúc MVC.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Đọc tài liệu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>LAB211_...docx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và vẽ sơ đồ Class Diagram bằng PlantUML.</t>
-    </r>
-  </si>
-  <si>
-    <t>AI sinh ra code sơ đồ lớp phân 3 tầng cơ bản (Model, Repo, Controller), đặt đúng các hàm Lock vào tầng Repository.</t>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Nhận thấy sơ đồ AI vẽ đúng logic OOP nhưng cấu trúc package chưa giống thực tế thư mục trên IDE của nhóm.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Decision: Cần cung cấp hình ảnh cấu trúc project thực tế để AI map lại code.</t>
-    </r>
-  </si>
-  <si>
-    <t>Code PlantUML version 1.</t>
-  </si>
-  <si>
-    <t>Class Diagram Detailing</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ảnh chụp thư mục IDE có thêm package </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>exception</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>view</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>enums</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> nhưng AI chưa vẽ.</t>
-    </r>
-  </si>
-  <si>
-    <t>"phần class diagram chưa đủ như hình tôi đã gửi đây" (Kèm ảnh chụp cấu trúc IDE</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI cập nhật code, vẽ thêm package </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>exception</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> với các lớp Custom Exception, mở rộng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>view</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>controller</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Phát hiện AI bị "ảo giác" (sót package </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) do góc chụp màn hình IDE bị cắt mất phần bên phải.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Contextualization: Báo cáo cần phản ánh đầy đủ thực thể.
-Decision: Chụp bù góc màn hình bị thiếu gửi cho AI.</t>
-    </r>
-  </si>
-  <si>
-    <t>Ảnh chụp đối chiếu IDE &amp; Code version 2.</t>
-  </si>
-  <si>
-    <t>Model Recovery</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Phần </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (chứa các Entity cốt lõi) bị mất, sơ đồ bị khuyết một nửa.</t>
-    </r>
-  </si>
-  <si>
-    <t>"bên góc này vẫn thiếu nè" (Kèm ảnh góc phải màn hình</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI nhận diện các class </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Customer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Product</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>... và merge lại thành bản Code MVC hoàn chỉnh ghép 2 nửa màn hình.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Creative Synthesis:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Không ngồi gõ tay lại từng class mà dùng tư duy chia để trị, đưa từng phần nhỏ cho AI tổng hợp thành bản full.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Decision: Chấp nhận bản code full để đem đi render ảnh.</t>
-    </r>
-  </si>
-  <si>
-    <t>Code PlantUML version 3 (Full Packages).</t>
   </si>
   <si>
     <t>DEBUGGING</t>
@@ -1149,207 +802,6 @@
     </r>
   </si>
   <si>
-    <t>Omission / Context Loss</t>
-  </si>
-  <si>
-    <t>Sơ đồ Class Diagram đã vẽ đầy đủ cấu trúc MVC của project.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sơ đồ bị khuyết hoàn toàn package </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (chứa các Entity lõi) do ảnh chụp đầu vào bị cắt mép.</t>
-    </r>
-  </si>
-  <si>
-    <t>Đối chiếu sơ đồ AI sinh ra với cấu trúc thư mục thực tế trên IDE.</t>
-  </si>
-  <si>
-    <t>Bổ sung hình chụp góc bị khuất và yêu cầu AI merge lại thành bản kiến trúc đầy đủ.</t>
-  </si>
-  <si>
-    <t>Logic Flaw / Unoptimized Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Đoạn code </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>DataGenerator</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> có thể sinh 10,000 dòng CSV an toàn bằng cách nạp hết vào </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>List&lt;T&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Đẩy 10,000+ object lên RAM cùng lúc gây nguy cơ tràn bộ nhớ (OutOfMemoryError) trên máy cấu hình thấp.</t>
-  </si>
-  <si>
-    <t>Review logic lưu trữ và đánh giá Big O (Space Complexity).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Xóa logic của AI. Tự viết lại cơ chế Batch Processing (chia lô), cứ 500 object thì </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>flush()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> xuống ổ cứng 1 lần.</t>
-    </r>
-  </si>
-  <si>
-    <t>Logic Flaw / Infinite Loop</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cơ chế </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Optimistic Lock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tự động retry 3 lần thành công khi bị lệch version.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vòng lặp </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>while</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bị lỗi vô hạn (Infinite Loop) do AI quên lệnh gọi đọc lại data (fetch new version) từ file CSV.</t>
-    </r>
-  </si>
-  <si>
-    <t>Chạy debug / Test tay thấy thread bị treo cứng khi có tranh chấp (Race Condition).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sửa tay đưa hàm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>findById()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vào ngay dòng đầu tiên bên trong vòng lặp </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>while</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để cập nhật version mới nhất.</t>
-    </r>
-  </si>
-  <si>
     <t>CODE GENERATION</t>
   </si>
   <si>
@@ -1709,6 +1161,289 @@
       <t xml:space="preserve">
 Decision: Áp dụng khóa theo block ID sản phẩm, tốc độ TPS lập tức tăng vọt gấp 3 lần.</t>
     </r>
+  </si>
+  <si>
+    <t>EXPLANATION</t>
+  </si>
+  <si>
+    <t>Simulator / Thread Synchronization</t>
+  </si>
+  <si>
+    <t>Cần công cụ ép hàng trăm luồng khách hàng bấm "Mua" tại đúng một mili-giây để ép hệ thống lỗi âm kho.</t>
+  </si>
+  <si>
+    <t>"Giải thích cách dùng ExecutorService và CountDownLatch để ép 500 threads bắt đầu chạy cùng một lúc."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI tư vấn dùng 3 rào chắn: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>readyLatch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>startLatch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (như tiếng súng bắt đầu), và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>doneLatch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đợi hoàn thành.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cấu trúc 3 rào chắn CountDownLatch trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SimulatorController.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thuật toán AI phân bổ rào chắn tốt nhưng thiếu bước dọn dẹp. Nếu không đóng Thread Pool, chương trình Java sẽ chạy ngầm không tắt được.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Decision: Thêm lệnh executor.shutdown() và awaitTermination() sau khi rào chắn doneLatch mở khóa.</t>
+    </r>
+  </si>
+  <si>
+    <t>Metrics / TPS Calculation</t>
+  </si>
+  <si>
+    <t>Kết quả thông lượng (TPS) đo được báo cáo sai do bị dính cả thời gian hệ điều hành cấp phát luồng.</t>
+  </si>
+  <si>
+    <t>"Code tính thời gian System.currentTimeMillis() của tôi bị sai vì nó đo luôn cả lúc Init Thread. Sửa công thức tính TPS lại."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI hướng dẫn dời biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>startTime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> xuống ngay sau lệnh nổ súng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>startLatch.countDown()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, và dời </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>endTime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ra sau </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>doneLatch.await()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bảng ASCII in kết quả ở Console và công thức đo TPS.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận thức được việc Benchmark hiệu năng phải loại trừ thời gian khởi động (warm-up time) thì số liệu mới trung thực.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Creative Synthesis: Format lại kết quả in ra console dưới dạng bảng ASCII để dễ so sánh 4 cơ chế trực quan.
+Decision: Chốt công thức TPS = Total Success Orders / Time.</t>
+    </r>
+  </si>
+  <si>
+    <t>Performance Hallucination</t>
+  </si>
+  <si>
+    <t>AI đề xuất dùng Reflection để tự động map tất cả Entity từ CSV.</t>
+  </si>
+  <si>
+    <t>Reflection hoạt động đúng nhưng gây giảm hiệu năng khi xử lý lượng dữ liệu lớn. Không phù hợp cho hệ thống TPS cao.</t>
+  </si>
+  <si>
+    <t>Benchmark đọc/ghi CSV với số lượng bản ghi lớn.</t>
+  </si>
+  <si>
+    <t>Thiết kế Abstract CsvRepository và BaseEntity để giảm phụ thuộc Reflection.</t>
+  </si>
+  <si>
+    <t>Scalability Hallucination</t>
+  </si>
+  <si>
+    <t>AI tạo toàn bộ 10.000+ object trong RAM rồi mới ghi file CSV.</t>
+  </si>
+  <si>
+    <t>Cách này có thể gây OutOfMemoryError trên máy cấu hình thấp.</t>
+  </si>
+  <si>
+    <t>Theo dõi Memory Usage khi sinh dữ liệu lớn.</t>
+  </si>
+  <si>
+    <t>Chuyển sang Batch Processing, ghi file từng 500 dòng và giải phóng bộ nhớ định kỳ.</t>
+  </si>
+  <si>
+    <t>Concurrency Hallucination</t>
+  </si>
+  <si>
+    <t>AI giải thích dùng synchronized ở cấp phương thức là đủ an toàn.</t>
+  </si>
+  <si>
+    <t>Method-level lock làm toàn bộ giao dịch bị nghẽn, TPS giảm mạnh (~80%).</t>
+  </si>
+  <si>
+    <t>Chạy benchmark đa luồng và đo TPS.</t>
+  </si>
+  <si>
+    <t>Chuyển sang Block-level Lock theo Product ID: synchronized(productId.intern()).</t>
   </si>
 </sst>
 </file>
@@ -1963,10 +1698,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2255,11 +1986,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="29.90625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
@@ -2274,17 +2005,17 @@
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
     </row>
-    <row r="3" spans="1:6" ht="18">
+    <row r="3" spans="1:6" ht="18.5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2292,26 +2023,26 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="22.8" customHeight="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.2" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.5">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2352,7 +2083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18">
+    <row r="15" spans="1:6" ht="18.5">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -2421,7 +2152,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:4" ht="18.5">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -2493,11 +2224,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
@@ -2529,7 +2260,7 @@
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
-    <row r="3" spans="1:13" ht="40.049999999999997" customHeight="1">
+    <row r="3" spans="1:13" ht="40" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>40</v>
       </c>
@@ -2555,130 +2286,86 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A4" s="7">
+    <row r="4" spans="1:13" ht="21" customHeight="1">
+      <c r="A4" s="7"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A5" s="7"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:13" ht="24.5" customHeight="1">
+      <c r="A6" s="7"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:13" ht="117.65" customHeight="1">
+      <c r="A7" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B7" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="G7" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="H7" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="19" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="80" customHeight="1">
+      <c r="A8" s="7">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="D8" s="19" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="F8" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G8" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="H8" s="19" t="s">
         <v>131</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="117.6" customHeight="1">
-      <c r="A7" s="7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A8" s="7">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>153</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -2686,30 +2373,30 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
     </row>
-    <row r="9" spans="1:13" ht="79.95" customHeight="1">
+    <row r="9" spans="1:13" ht="80" customHeight="1">
       <c r="A9" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -2717,30 +2404,30 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:13" ht="79.95" customHeight="1">
+    <row r="10" spans="1:13" ht="80" customHeight="1">
       <c r="A10" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -2748,115 +2435,146 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:13" s="19" customFormat="1" ht="126.6" customHeight="1">
+    <row r="11" spans="1:13" s="19" customFormat="1" ht="126.65" customHeight="1">
       <c r="A11" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="19" customFormat="1" ht="80" customHeight="1">
       <c r="A12" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="19" customFormat="1" ht="151.80000000000001" customHeight="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="19" customFormat="1" ht="151.75" customHeight="1">
       <c r="A13" s="23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" ht="79.95" customHeight="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="19" customFormat="1" ht="120.5" customHeight="1">
+      <c r="A14" s="7">
+        <v>8</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="19" customFormat="1" ht="155" customHeight="1">
+      <c r="A15" s="7">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="80" customHeight="1">
       <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1">
+    <row r="17" spans="1:8" ht="80" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2866,7 +2584,7 @@
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1">
+    <row r="18" spans="1:8" ht="80" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2876,7 +2594,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1">
+    <row r="19" spans="1:8" ht="80" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2886,7 +2604,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1">
+    <row r="20" spans="1:8" ht="80" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2896,7 +2614,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1">
+    <row r="21" spans="1:8" ht="80" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2906,7 +2624,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1">
+    <row r="22" spans="1:8" ht="80" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2916,7 +2634,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1">
+    <row r="23" spans="1:8" ht="80" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2926,7 +2644,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1">
+    <row r="24" spans="1:8" ht="80" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2936,7 +2654,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1">
+    <row r="25" spans="1:8" ht="80" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2946,7 +2664,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1">
+    <row r="26" spans="1:8" ht="80" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2968,7 +2686,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2995,7 +2713,7 @@
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
     </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
+    <row r="3" spans="1:6" ht="40" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>55</v>
       </c>
@@ -3015,81 +2733,73 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="35.4" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="92.4" customHeight="1">
+    <row r="4" spans="1:6" s="19" customFormat="1" ht="103" customHeight="1">
+      <c r="A4" s="7">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="19" customFormat="1" ht="92.4" customHeight="1">
       <c r="A5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="7"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A6" s="7">
+        <v>7</v>
+      </c>
       <c r="B6" s="19" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>180</v>
-      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="7"/>
@@ -3227,75 +2937,75 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18">
+    <row r="30" spans="1:6" ht="18.5">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="29">
       <c r="A32" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="29">
+      <c r="A33" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="7" t="s">
+    </row>
+    <row r="34" spans="1:3" ht="29">
+      <c r="A34" s="7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.8">
-      <c r="A33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="7" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="29">
+      <c r="A35" s="7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.8">
-      <c r="A34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="7" t="s">
+    </row>
+    <row r="36" spans="1:3" ht="43.5">
+      <c r="A36" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="28.8">
-      <c r="A35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="43.2">
-      <c r="A36" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3310,7 +3020,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -3320,7 +3030,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -3328,207 +3038,207 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
     </row>
-    <row r="4" spans="1:4" ht="18">
+    <row r="4" spans="1:4" ht="18.5">
       <c r="A4" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18">
+    <row r="12" spans="1:4" ht="18.5">
       <c r="A12" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6">
+    <row r="20" spans="1:4" ht="15.5">
       <c r="A20" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.5">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="43.5">
       <c r="A27" s="17" t="s">
         <v>40</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC47191-6C60-4379-B382-A35143093859}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50530679-521A-4194-B890-D9C49FA7E28B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="216">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -220,18 +220,6 @@
   </si>
   <si>
     <t>Fabrication</t>
-  </si>
-  <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -1708,6 +1696,248 @@
       </rPr>
       <t xml:space="preserve">
 Decision: Áp dụng khóa theo block ID sản phẩm, tốc độ TPS lập tức tăng vọt gấp 3 lần.</t>
+    </r>
+  </si>
+  <si>
+    <t>Problem-Solving</t>
+  </si>
+  <si>
+    <t>View &amp; Validation</t>
+  </si>
+  <si>
+    <t>Cần ràng buộc dữ liệu đầu vào (email, số điện thoại) khắt khe ở tầng View để tránh lưu file CSV rác.</t>
+  </si>
+  <si>
+    <t>Cho xin mẫu Regex để bắt lỗi email và số điện thoại chuẩn Việt Nam trong Java</t>
+  </si>
+  <si>
+    <t>AI cung cấp bộ Regex khá phức tạp và đa dụng, bao gồm cả các mã vùng quốc tế và format email lạ.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận thấy Regex của AI quá rườm rà so với scope dự án (chỉ cần sđt 9-11 số), em đã chủ động cắt tỉa lại chuỗi Pattern cho gọn nhẹ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Em quyết định đặt nó ở AdminCustomerView để chặn rác ngay ở cửa ngõ hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Các biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EMAIL_PATTERN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PHONE_PATTERN</t>
+    </r>
+  </si>
+  <si>
+    <t>Tầng Repository &amp; Logic Auth</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cần tối ưu thuật toán sinh ID tự động và hiểu rõ luồng kiểm tra trùng lặp email khi đăng ký từ file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>customers.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Giải thích code CustomerRepository cho tôi, phần tự động sinh ID và hàm login</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI giải thích chi tiết cơ chế Java Stream API để lấy ID lớn nhất. Đồng thời, AI phân tích việc đặt logic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>check banned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ở Repo là vi phạm nguyên tắc SRP của MVC.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Em ghi nhận lỗi thiết kế (Technical Debt) này. Em tạm giữ ở Repo để đảm bảo tiến độ test I/O Tuần 3, nhưng đã note lại kịch bản để tự bảo vệ và giải thích lỗi thiết kế kiến trúc này trước giảng viên.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomerRepository.java</t>
+    </r>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Chức năng Admin (Ban/Unban)</t>
+  </si>
+  <si>
+    <t>Xây dựng chức năng khóa/mở khóa tài khoản khách hàng ở giao diện Admin sao cho tối ưu, tránh lặp code.</t>
+  </si>
+  <si>
+    <t>Giải thích code phần AdminCustomerView và cách xử lý thay đổi trạng thái user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI gợi ý luồng xử lý trạng thái user thành 2 hàm riêng biệt là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ban()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unban()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Em chủ động bác bỏ gợi ý viết 2 hàm riêng lẻ. Em tự áp dụng tư duy Clean Code để gộp chung thành 1 hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>setCustomerStatus(String status)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, giúp tái sử dụng code và dễ bảo trì hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AdminCustomerView.java</t>
     </r>
   </si>
 </sst>
@@ -1932,18 +2162,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2265,7 +2495,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
@@ -2281,10 +2511,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2292,7 +2522,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.8" customHeight="1">
@@ -2300,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.2" customHeight="1">
@@ -2308,7 +2538,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
@@ -2498,15 +2728,15 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="38.5546875" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="25"/>
@@ -2518,7 +2748,7 @@
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="25"/>
@@ -2563,22 +2793,22 @@
         <v>50</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="H4" s="19" t="s">
         <v>123</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="100.05" customHeight="1">
@@ -2587,22 +2817,22 @@
         <v>52</v>
       </c>
       <c r="C5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="H5" s="19" t="s">
         <v>129</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="100.05" customHeight="1">
@@ -2611,22 +2841,22 @@
         <v>50</v>
       </c>
       <c r="C6" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="H6" s="19" t="s">
         <v>135</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="117.6" customHeight="1">
@@ -2634,25 +2864,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="G7" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="H7" s="19" t="s">
         <v>142</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="79.95" customHeight="1">
@@ -2660,25 +2890,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="G8" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="H8" s="19" t="s">
         <v>149</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>153</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -2691,25 +2921,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="H9" s="19" t="s">
         <v>155</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>159</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -2725,22 +2955,22 @@
         <v>50</v>
       </c>
       <c r="C10" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="H10" s="19" t="s">
         <v>161</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>165</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -2753,25 +2983,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="H11" s="19" t="s">
         <v>183</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
@@ -2782,22 +3012,22 @@
         <v>50</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>188</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="19" customFormat="1" ht="151.80000000000001" customHeight="1">
@@ -2805,56 +3035,98 @@
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C13" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>194</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="79.95" customHeight="1">
       <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="B14" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="79.95" customHeight="1">
       <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" ht="79.95" customHeight="1">
+      <c r="B15" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
       <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="B16" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1">
       <c r="A17" s="7"/>
@@ -2976,7 +3248,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="25"/>
@@ -2986,7 +3258,7 @@
       <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="25"/>
@@ -3016,79 +3288,71 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="35.4" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="92.4" customHeight="1">
       <c r="A5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="19" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1">
+      <c r="A6" s="7">
+        <v>8</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="C6" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1">
+      <c r="A7" s="7">
+        <v>14</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="C7" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
@@ -3229,18 +3493,18 @@
     </row>
     <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8">
@@ -3248,54 +3512,54 @@
         <v>61</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3319,8 +3583,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="27" t="s">
-        <v>84</v>
+      <c r="A1" s="26" t="s">
+        <v>80</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -3328,7 +3592,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -3336,185 +3600,185 @@
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
@@ -3522,13 +3786,13 @@
         <v>40</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="8_{D78745D7-9B6E-428F-900A-C9D5AB7AEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50530679-521A-4194-B890-D9C49FA7E28B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E990FD8B-096B-4DDF-97C2-A8056726A089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="294">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Hallucination Detected:</t>
   </si>
   <si>
-    <t>[Count]</t>
-  </si>
-  <si>
     <t>AI TOOLS USED</t>
   </si>
   <si>
@@ -183,18 +180,78 @@
     <t>001</t>
   </si>
   <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>Cần chia nhỏ requirement</t>
+  </si>
+  <si>
+    <t>Break down student management into modules</t>
+  </si>
+  <si>
+    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
+  </si>
+  <si>
+    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
+Contextualization: Project scope nhỏ, chỉ cần core functions.
+Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
+Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
+  </si>
+  <si>
+    <t>Screenshot comparison 10 vs 5</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
+    <t>Search by name quá chậm với 10K records</t>
+  </si>
+  <si>
+    <t>How to optimize search for player name in 10,000 records?</t>
+  </si>
+  <si>
+    <t>AI suggested Binary Search with O(log n) complexity</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
+Contextualization: Requirements yêu cầu partial name search.
+Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
+Decision: Chọn HashMap trade-off memory cho speed.</t>
+  </si>
+  <si>
+    <t>Code snippet + timing comparison</t>
+  </si>
+  <si>
     <t>003</t>
   </si>
   <si>
     <t>VERIFICATION</t>
   </si>
   <si>
+    <t>Literature Review</t>
+  </si>
+  <si>
+    <t>Cần verify paper AI cite</t>
+  </si>
+  <si>
+    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
+  </si>
+  <si>
+    <t>AI confirmed it exists and provided summary</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
+Contextualization: AI fabricated paper to answer my question.
+Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
+Decision: Replace with verified paper from Google Scholar.</t>
+  </si>
+  <si>
+    <t>Google Scholar screenshot</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -301,9 +358,6 @@
   </si>
   <si>
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
-  </si>
-  <si>
-    <t>☐</t>
   </si>
   <si>
     <t>2</t>
@@ -1035,36 +1089,36 @@
     <t>Bản render SVG Final vuông vức hoàn hảo.</t>
   </si>
   <si>
-    <t>Repository / File I/O</t>
-  </si>
-  <si>
-    <t>Phải viết code đọc/ghi CSV cho 7 Entity khác nhau. Cần giải pháp tránh lặp code (Duplicate code).</t>
-  </si>
-  <si>
-    <t>"Viết class CsvRepository dùng Generics trong Java để đọc ghi file CSV cho tất cả các Entity tự động bằng Reflection."</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI cung cấp class dùng thư viện </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>java.lang.reflect</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để tự động map các cột CSV vào các thuộc tính (fields) của Object.</t>
-    </r>
+    <t>Tuần 3: Tầng Repository &amp; Logic MVC</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cần hiểu code tự sinh ID và tối ưu luồng kiểm tra trùng lặp email khi đăng ký từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>customers.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Giải thích code CustomerRepository cho tôi"</t>
+  </si>
+  <si>
+    <t>AI giải thích chi tiết cơ chế Java Stream API để sinh ID. Đồng thời phát hiện lỗi thiết kế: nhét logic check banned/email vào Repo là vi phạm SRP.</t>
   </si>
   <si>
     <r>
@@ -1078,7 +1132,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Nhận thấy dùng Reflection liên tục khi đọc/ghi 10.000 dòng dữ liệu sẽ làm giảm hiệu năng hệ thống cực kỳ nghiêm trọng (Bottleneck).</t>
+      <t xml:space="preserve"> Nhận thấy AI chỉ ra đúng lỗi vi phạm nguyên tắc Đơn trách nhiệm (SRP) của MVC.</t>
     </r>
     <r>
       <rPr>
@@ -1090,22 +1144,22 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Contextualization: Dự án yêu cầu đo lường TPS khắt khe nên tốc độ File I/O là cốt lõi.
-Creative Synthesis: Hủy bỏ Reflection. Chuyển sang ép kiểu thông qua 2 hàm abstract toCsvLine() và fromCsvLine() ở BaseEntity.
-Decision: Tối ưu hóa tốc độ parse CSV bằng việc xử lý chuỗi thủ công trong từng model.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Source code abstract class </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>CsvRepository</t>
+Contextualization: Dự án bắt buộc tuân thủ kiến trúc phân tầng, nếu để Repo xử lý logic sẽ bị trừ điểm.
+Creative Synthesis: Tách hoàn toàn logic kiểm tra dữ liệu và trạng thái tài khoản ra khỏi lớp I/O.
+Decision: Tạo mới CustomerController làm bộ não xử lý nghiệp vụ, biến CustomerRepository thành class thuần đọc/ghi file.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomerController.java</t>
     </r>
     <r>
       <rPr>
@@ -1123,7 +1177,167 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>BaseEntity</t>
+      <t>CustomerRepository.java</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 3: Unit Test (Kiểm thử đơn vị)</t>
+  </si>
+  <si>
+    <t>Cần nghiệm thu thuật toán sinh ID tự động để đảm bảo dữ liệu không sai sót trước khi ráp vào luồng chính.</t>
+  </si>
+  <si>
+    <t>"Giải thích code cho tui đi" (kèm file CustomRepositoryTest.java)</t>
+  </si>
+  <si>
+    <r>
+      <t>AI phân tích vòng đời JUnit (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Before</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@After</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), giải thích cơ chế dọn dẹp thư mục và luồng test nhảy cóc ID.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Đánh giá cao việc dùng AI sinh boilerplate code cho JUnit, nhưng test case thực tế phải tự định nghĩa
+Contextualization: Yêu cầu tuần 3 cần độ chính xác 100% khi thao tác với file CSV. 
+Creative Synthesis: Kết hợp cấu trúc AI gợi ý để thiết lập kịch bản giả lập kho trống và kho có dữ liệu nhảy cóc trên thư mục test_data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision: Áp dụng kịch bản JUnit để tự động hóa việc test hàm generateNewCustomerId, tiết kiệm thời gian debug thủ công.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomRepositoryTest.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Passed xanh trên NetBeans 12)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 4: Chức năng Admin (Ban/Unban)</t>
+  </si>
+  <si>
+    <t>Xây dựng chức năng khóa/mở khóa tài khoản khách hàng ở giao diện Admin sao cho tối ưu, Clean Code.</t>
+  </si>
+  <si>
+    <t>"Fix tất cả các lỗi cho tôi luôn nhé" (sau khi bàn về việc xử lý thay đổi trạng thái user)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ban đầu AI gợi ý luồng xử lý trạng thái user thành 2 hàm riêng biệt là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ban()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unban()</t>
     </r>
     <r>
       <rPr>
@@ -1137,72 +1351,768 @@
     </r>
   </si>
   <si>
-    <t>Omission / Context Loss</t>
-  </si>
-  <si>
-    <t>Sơ đồ Class Diagram đã vẽ đầy đủ cấu trúc MVC của project.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sơ đồ bị khuyết hoàn toàn package </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (chứa các Entity lõi) do ảnh chụp đầu vào bị cắt mép.</t>
-    </r>
-  </si>
-  <si>
-    <t>Đối chiếu sơ đồ AI sinh ra với cấu trúc thư mục thực tế trên IDE.</t>
-  </si>
-  <si>
-    <t>Bổ sung hình chụp góc bị khuất và yêu cầu AI merge lại thành bản kiến trúc đầy đủ.</t>
-  </si>
-  <si>
-    <t>Logic Flaw / Unoptimized Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Đoạn code </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>DataGenerator</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> có thể sinh 10,000 dòng CSV an toàn bằng cách nạp hết vào </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>List&lt;T&gt;</t>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>setCustomerStatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomerController.java</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking: Nhận thấy đề xuất của AI gây lặp code (Code Duplication) không cần thiết.
+Contextualization: Code trên NetBeans cần phải gọn gàng, dễ bảo trì để thuận lợi khi bảo vệ vấn đáp. 
+Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tự tái cấu 
+Decision: Quyết định chỉ dùng 1 hàm duy nhất setCustomerStatus(String status) để xử lý triệt để bài toán.trúc lại đề xuất của AI, gộp chung logic cập nhật trạng thái "ACTIVE"/"BANNED" thông qua tham số.
+Decision: Quyết định chỉ dùng 1 hàm duy nhất setCustomerStatus(String status) để xử lý triệt để bài toán.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 4: Validation Tầng View</t>
+  </si>
+  <si>
+    <t>Cần ràng buộc dữ liệu đầu vào (email, số điện thoại) khắt khe ở tầng View để tránh lưu rác vào file CSV.</t>
+  </si>
+  <si>
+    <t>"Cho xin mẫu Regex để bắt lỗi email và số điện thoại chuẩn trong Java"</t>
+  </si>
+  <si>
+    <t>AI cung cấp bộ Regex chuẩn quốc tế, khá rườm rà và bao quát nhiều mã vùng/định dạng phức tạp.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Đánh giá Regex của AI là quá mức cần thiết (Over-engineering) so với scope của dự án.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Đồ án Flash Sale chỉ yêu cầu kiểm tra tính hợp lệ cơ bản của SĐT (9-11 số) và Email tiêu chuẩn.
+Creative Synthesis: Tự lọc bỏ các pattern mã vùng quốc tế thừa thãi, tự rút gọn lại biểu thức chính quy.
+Decision: Chốt sử dụng chuỗi Regex gọn nhẹ (VD: ^\d{9,11}$) đặt tại AdminCustomerView để tối ưu tài nguyên và dễ giải thích.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EMAIL_PATTERN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PHONE_PATTERN</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 3: File I/O &amp; Exception</t>
+  </si>
+  <si>
+    <r>
+      <t>Cần xử lý lỗi ép kiểu (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>NumberFormatException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) khi đọc dữ liệu từ CSV để tự động sinh ID khách hàng.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Giải thích ý nghĩa đoạn try-catch trong hàm mapToInt khi sinh ID"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI giải thích nếu file CSV có dữ liệu rác, lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Integer.parseInt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ gây crash app; catch lỗi trả về 0 để hệ thống chạy tiếp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận thấy nếu lạm dụng việc trả về 0 liên tục khi file lỗi nặng có thể dẫn đến sinh ID trùng lặp.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Đặc tả yêu cầu Customer ID (C-XXXXX) phải là duy nhất trên toàn hệ thống.
+Creative Synthesis: Nhận ra try-catch chỉ là chốt chặn cuối. Cần kết hợp với hệ thống Regex của Tuần 4 chặn rác từ đầu vào.
+Decision: Giữ nguyên logic trả về 0 của AI ở tầng Data, nhưng tăng cường ràng buộc ở tầng View để đảm bảo luồng Exception gần như không bao giờ xảy ra.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khối try-catch trong hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>generateNewCustomerId</t>
+    </r>
+  </si>
+  <si>
+    <t>Tầng Repository (Decompile)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phát hiện file xử lý logic sinh ID bị dịch ngược thành </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>var0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>var1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, cần hiểu rõ để giải thích.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Giải thích đoạn code bị decompile này cho tôi" (Kèm code từ FernFlower)</t>
+  </si>
+  <si>
+    <r>
+      <t>AI ánh xạ các biến bytecode (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>var0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>var1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) về đúng tên gốc (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>maxId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) và giải thích luồng xử lý Lambda Expression của JVM.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận diện được cơ chế tự động tối ưu hóa của máy ảo JVM khi biên dịch code.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Trong buổi bảo vệ LAB211, giảng viên có thể dùng tool dịch ngược để test độ hiểu bài thay vì nhìn file gốc.
+Creative Synthesis: Kết hợp kiến thức Java Stream với bản đồ ánh xạ của AI để diễn dịch lại đúng logic cắt chuỗi gốc.
+Decision: Tự tin dùng kịch bản phân tích .class này làm minh chứng nắm vững core logic thay vì chỉ học vẹt mã nguồn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomerRepository.class</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 5: Entry Point &amp; Dependency Injection</t>
+  </si>
+  <si>
+    <t>Cần ráp nối các thành phần rời rạc (Repository, Controller, View) thành ứng dụng hoàn chỉnh nhưng code khởi tạo đang lộn xộn, thiếu an toàn.</t>
+  </si>
+  <si>
+    <t>"giải thích code cho tôi đi cái này là tuần 5 6 nè" và "có lỗi nào ko fix cho tôi đi"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI phân tích kiến trúc kết nối (Wiring) và phát hiện mã nguồn thiếu khối </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>try-catch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bảo vệ luồng I/O ở hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, dễ gây crash toàn hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận định việc khởi tạo hàng loạt class đọc file CSV cùng lúc tiềm ẩn rủi ro rất cao nếu file bị xóa hoặc lỗi.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Đồ án là ứng dụng Console, nếu crash giữa chừng người dùng sẽ không biết vì sao.
+Creative Synthesis: Gom toàn bộ luồng khởi tạo và Dependency Injection vào một khối try-catch thống nhất ở cấp cao nhất.
+Decision: Cập nhật file FlashSaleApplication.java, bổ sung xử lý lỗi thân thiện để hệ thống báo lỗi từ tốn thay vì sập nguồn (Crash).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FlashSaleApplication.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (hàm main)</t>
+    </r>
+  </si>
+  <si>
+    <t>UI &amp; Console Encoding</t>
+  </si>
+  <si>
+    <t>Giao diện Console trên Windows bị lỗi font tiếng Việt (hiện dấu ???) và ký hiệu tiền tệ (₫) bị sai lệch.</t>
+  </si>
+  <si>
+    <t>"làm code để luôn thấy dòng Active code page: 65001"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI đề xuất 2 giải pháp: tạo file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>run.bat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chứa lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>chcp 65001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProcessBuilder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gọi ngầm CMD trực tiếp từ Java để ép bảng mã UTF-8.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Locale.setDefault</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>netbeans.conf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Việc dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ProcessBuilder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cmd.exe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ khiến code bị phụ thuộc vào Windows, mất tính đa nền tảng của Java.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Giảng viên thường chấm bài bằng cách chạy trực tiếp trên IDE Apache NetBeans 12. 
+Creative Synthesis: Kết hợp lệnh set Locale tiền tệ với việc cấu hình tham số -Dfile.encoding=UTF-8 cho JVM khi chạy.
+Decision: Lựa chọn phương án an toàn nhất: Cấu hình bảng mã qua JVM/NetBeans và thiết lập Locale("vi", "VN") trong code để UI chuẩn xác 100%.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Business Logic &amp; Data Integrity</t>
+  </si>
+  <si>
+    <t>Xử lý bài toán hóc búa (giảng viên hỏi bẫy): Hệ thống có cho phép thêm sản phẩm vào sự kiện Flash Sale đã quá hạn hay không?</t>
+  </si>
+  <si>
+    <t>"thầy hỏi nếu sự kiện đó hết hạng cho được bỏ sản phẩm vào sự kiện ko"</t>
+  </si>
+  <si>
+    <r>
+      <t>AI xác nhận là KHÔNG và cung cấp giải pháp kiểm tra trạng thái (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) hoặc dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>LocalDateTime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để chặn luồng lưu dữ liệu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logic chặn sự kiện quá hạn trong luồng Thêm sản phẩm</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phân biệt rõ giữa lỗi lưu trữ (Data I/O) và lỗi nghiệp vụ. Chức năng lưu file vẫn chạy được không có nghĩa là nghiệp vụ đúng.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Tính toàn vẹn dữ liệu trong thương mại điện tử yêu cầu sự kiện đã "ENDED" phải bị đóng băng hoàn toàn.
+Creative Synthesis: Thiết kế lớp khiên bảo vệ (Validation) chặn request ngay tại Controller trước khi nó chạm tới Database (CSV).
+Decision: Bổ sung logic kiểm tra trạng thái sự kiện, ném ra IllegalStateException từ chối thao tác nếu sự kiện đã hết hạn.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chức năng Admin (Xem Doanh thu)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cần thống kê, tổng hợp và sắp xếp danh sách doanh thu Flash Sale từ cao xuống thấp nhưng dữ liệu gốc nằm rải rác trong list </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Order</t>
     </r>
     <r>
       <rPr>
@@ -1216,160 +2126,88 @@
     </r>
   </si>
   <si>
-    <t>Đẩy 10,000+ object lên RAM cùng lúc gây nguy cơ tràn bộ nhớ (OutOfMemoryError) trên máy cấu hình thấp.</t>
-  </si>
-  <si>
-    <t>Review logic lưu trữ và đánh giá Big O (Space Complexity).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Xóa logic của AI. Tự viết lại cơ chế Batch Processing (chia lô), cứ 500 object thì </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>flush()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> xuống ổ cứng 1 lần.</t>
-    </r>
-  </si>
-  <si>
-    <t>Logic Flaw / Infinite Loop</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cơ chế </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Optimistic Lock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tự động retry 3 lần thành công khi bị lệch version.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vòng lặp </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>while</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bị lỗi vô hạn (Infinite Loop) do AI quên lệnh gọi đọc lại data (fetch new version) từ file CSV.</t>
-    </r>
-  </si>
-  <si>
-    <t>Chạy debug / Test tay thấy thread bị treo cứng khi có tranh chấp (Race Condition).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sửa tay đưa hàm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>findById()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vào ngay dòng đầu tiên bên trong vòng lặp </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>while</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để cập nhật version mới nhất.</t>
-    </r>
-  </si>
-  <si>
-    <t>CODE GENERATION</t>
-  </si>
-  <si>
-    <t>Data Generator Tool</t>
-  </si>
-  <si>
-    <t>Đề bài yêu cầu tạo file CSV mồi có ≥ 10.000 dòng. Cần sinh dữ liệu giả (Mock data) nhưng không làm treo máy.</t>
-  </si>
-  <si>
-    <t>"Viết hàm DataGenerator sinh 5000 Products và 2000 Customers lưu ra file CSV."</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI viết vòng lặp tạo toàn bộ object ném vào một </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>List&lt;T&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> khổng lồ, sau đó mới dùng stream ghi ra file CSV cùng một lúc.</t>
+    <t>"Viết hàm tính tổng doanh thu và sắp xếp giảm dần trong Java"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI đề xuất dùng vòng lặp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để tính tổng, sau đó dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Collections.sort()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Comparator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tùy chỉnh để sắp xếp List.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>viewRevenueReport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong tầng Controller/View</t>
     </r>
   </si>
   <si>
@@ -1384,25 +2222,25 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Nhận thấy thuật toán của AI lưu 10.000+ object trên RAM cùng lúc dễ gây tràn bộ nhớ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>OutOfMemoryError</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) trên máy cấu hình thấp.</t>
+      <t xml:space="preserve"> Việc dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Collections.sort()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ làm thay đổi thứ tự của List gốc lưu trong RAM, có thể gây lỗi cho các chức năng khác đang dùng chung List này.</t>
     </r>
     <r>
       <rPr>
@@ -1414,21 +2252,121 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Creative Synthesis: Hủy cách làm của AI, tự thiết kế lại thành kỹ thuật Batch Processing (Chia lô). Cứ tạo 500 dòng là flush() xuống ổ cứng và làm sạch list.
-Decision: Chốt phương án sinh dữ liệu theo lô để tối ưu RAM.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Code vòng lặp sinh dữ liệu trong </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>DataGenerator.java</t>
+Contextualization: Đồ án khuyến khích sử dụng cú pháp hiện đại của Java 8 để tối ưu và làm gọn mã nguồn.
+Creative Synthesis: Từ chối cách dùng vòng lặp cổ điển. Ứng dụng Stream API để nhóm dữ liệu (grouping) và sắp xếp mà không chạm vào List gốc.
+Decision: Tự viết lại logic bằng chuỗi stream().sorted().collect(Collectors.toList()) tạo ra một danh sách bản sao (copy) chỉ phục vụ cho việc hiển thị ở ReportView, an toàn tuyệt đối.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Tuần 6: Logic Nghiệp vụ (Ban/Unban)</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra xem chức năng cập nhật trạng thái "BANNED" khách hàng có lỗ hổng logic (Edge case) nào không.</t>
+  </si>
+  <si>
+    <t>"Gợi ý các test case để test chức năng khóa tài khoản user"</t>
+  </si>
+  <si>
+    <t>AI liệt kê các kịch bản cơ bản: Nhập ID đúng, ID sai, ID bị bỏ trống, phân biệt hoa/thường.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Logic chặn tự khóa (Self-Ban) trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CustomerController</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận ra AI đã bỏ qua một kịch bản kinh điển dẫn đến mất quyền kiểm soát: Người dùng có quyền Admin tự khóa chính tài khoản của mình.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Contextualization: Trong hệ thống, thao tác Ban/Unban được thực hiện bởi người đang đăng nhập. Nếu tự "hủy" chính mình, hệ thống sẽ rối loạn trạng thái (Session).
+Creative Synthesis: Tự thiết kế thêm một chốt chặn bảo mật ở tầng nghiệp vụ để đối chiếu ID mục tiêu với ID đang thao tác.
+Decision: Bổ sung câu lệnh if (targetId.equals(loggedInUser.getId())) throw new Exception("Không thể tự khóa tài khoản của chính mình!"); vào CustomerController để triệt tiêu hoàn toàn rủi ro này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logical Omission</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Code dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>line.split(",")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là đủ an toàn để tránh lỗi khi đọc file CSV.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu gặp dòng trống (blank line), lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>split</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gây lỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ArrayIndexOutOfBoundsException</t>
     </r>
     <r>
       <rPr>
@@ -1442,54 +2380,33 @@
     </r>
   </si>
   <si>
-    <t>Concurrency / FILE_LOCK</t>
-  </si>
-  <si>
-    <t>Cần khóa file cấp độ hệ điều hành (OS-level lock) để tránh đa luồng ghi đè file CSV cùng lúc gây hỏng dữ liệu.</t>
-  </si>
-  <si>
-    <t>"Làm sao dùng FileChannel trong Java nio để khóa file flash_items.csv an toàn khi có đa luồng?"</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI gợi ý gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>FileChannel.open()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và dùng lệnh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>channel.lock()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để block các luồng khác không cho phép ghi.</t>
-    </r>
+    <t>Chạy thử nghiệm thực tế (Dry-run) với file CSV chèn dòng trống.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bổ sung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>if (line.trim().isEmpty()) continue;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trước khi split.</t>
+    </r>
+  </si>
+  <si>
+    <t>Contextual Hallucination</t>
   </si>
   <si>
     <r>
@@ -1501,50 +2418,318 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>sellWithFileLock()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> chứa khối </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>try-finally</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> chặt chẽ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Phát hiện code AI thiếu cơ chế giải phóng tài nguyên. Nếu luồng đang ghi bị văng Exception, file sẽ bị khóa vĩnh viễn (Deadlock).</t>
+      <t>setCustomerStatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đã hoàn hảo, không cần thêm ràng buộc.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logic cho phép Admin tự khóa tài khoản chính mình (Self-lockout).</t>
+  </si>
+  <si>
+    <t>Phân tích luồng nghiệp vụ và bảo mật hệ thống.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thêm kiểm tra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>targetId.equals(loggedInAdminId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để chặn tự khóa.</t>
+    </r>
+  </si>
+  <si>
+    <t>Unsafe Implementation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đóng khóa file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FileLock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thủ công trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>finally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là phương án tốt nhất.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cách này vẫn gây Deadlock nếu Thread bị crash trước khi chạy đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>finally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đối chiếu với tài liệu Oracle Java NIO chính thức.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Viết lại hàm bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>try-with-resources</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo OS tự nhả khóa.</t>
+    </r>
+  </si>
+  <si>
+    <t>State Hallucination (Ảo giác trạng thái)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gợi ý dùng biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>private static int count = 0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đếm và tự động tăng ID cho khách hàng mới.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Biến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lưu trên RAM sẽ bị reset về 0 mỗi khi tắt chương trình. Lần bật app sau, ID sẽ quay về mức ban đầu gây trùng lặp dữ liệu trong file CSV.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kiểm thử thực tế: Tạo 2 user, tắt app, bật lại tạo thêm 1 user nữa thì hệ thống báo lỗi ghi đè ID.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thay đổi logic: Bắt buộc hệ thống quét file CSV đọc toàn bộ ID, tìm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>maxId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hiện tại rồi mới +1.</t>
+    </r>
+  </si>
+  <si>
+    <t>Contextual Hallucination (Ảo giác ngữ cảnh)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>setCustomerStatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đã hoàn hảo, có thể dùng trực tiếp để Ban/Unban tài khoản mà không cần thêm ràng buộc.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logic của AI cho phép người dùng Admin nhập mã ID của chính mình và set thành "BANNED", dẫn đến việc tự khóa tài khoản của bản thân (Self-lockout).</t>
+  </si>
+  <si>
+    <t>Phân tích luồng nghiệp vụ (Business Flow Analysis) đối chiếu với các tiêu chuẩn bảo mật phân quyền.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thêm lệnh kiểm tra: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>if (targetId.equals(loggedInAdminId)) throw new Exception("Không thể tự khóa!");</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào Controller.</t>
+    </r>
+  </si>
+  <si>
+    <t>API/Version Hallucination (Ảo giác phiên bản)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đề xuất sử dụng hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Files.readString(Path.of(...))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đọc toàn bộ nội dung file CSV nhanh gọn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Files.readString()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chỉ được hỗ trợ từ </t>
     </r>
     <r>
       <rPr>
@@ -1555,69 +2740,51 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-Contextualization: Xử lý đa luồng bắt buộc phải dọn dẹp tài nguyên (cleanup) cẩn thận.
-Decision: Bắt buộc bọc lệnh lock() trong khối try và gọi lock.release() ở khối finally.</t>
-    </r>
-  </si>
-  <si>
-    <t>Concurrency / SYNCHRONIZED</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cài đặt cơ chế JVM Lock, nhưng khi gắn từ khóa </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>synchronized</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vào phương thức </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>sell()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, thông lượng (TPS) giảm đến 80%.</t>
-    </r>
-  </si>
-  <si>
-    <t>"Tại sao dùng phương thức synchronized lại làm rớt TPS nghiêm trọng? Có cách nào tối ưu hơn không?"</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI giải thích do khóa cả phương thức (Method-level lock), khiến luồng mua sản phẩm A cũng phải chờ luồng mua sản phẩm B. Gợi ý đổi sang Block-level lock: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>synchronized(productId.intern())</t>
+      <t>Java 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trở lên. Môi trường đồ án bắt buộc dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trên NetBeans 12.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dán code vào IDE Apache NetBeans 12, trình biên dịch lập tức báo lỗi đỏ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cannot find symbol</t>
     </r>
     <r>
       <rPr>
@@ -1632,248 +2799,15 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Khối mã </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>synchronized(itemId.intern())</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> trong Repository.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Hiểu được sự tắc nghẽn (bottleneck) của khóa toàn cục. Thuật toán dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>intern()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> của AI rất thông minh vì nó chia sẻ chung String pool cho các ID sản phẩm giống nhau.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Decision: Áp dụng khóa theo block ID sản phẩm, tốc độ TPS lập tức tăng vọt gấp 3 lần.</t>
-    </r>
-  </si>
-  <si>
-    <t>Problem-Solving</t>
-  </si>
-  <si>
-    <t>View &amp; Validation</t>
-  </si>
-  <si>
-    <t>Cần ràng buộc dữ liệu đầu vào (email, số điện thoại) khắt khe ở tầng View để tránh lưu file CSV rác.</t>
-  </si>
-  <si>
-    <t>Cho xin mẫu Regex để bắt lỗi email và số điện thoại chuẩn Việt Nam trong Java</t>
-  </si>
-  <si>
-    <t>AI cung cấp bộ Regex khá phức tạp và đa dụng, bao gồm cả các mã vùng quốc tế và format email lạ.</t>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Nhận thấy Regex của AI quá rườm rà so với scope dự án (chỉ cần sđt 9-11 số), em đã chủ động cắt tỉa lại chuỗi Pattern cho gọn nhẹ</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Em quyết định đặt nó ở AdminCustomerView để chặn rác ngay ở cửa ngõ hệ thống.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Các biến </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>EMAIL_PATTERN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>PHONE_PATTERN</t>
-    </r>
-  </si>
-  <si>
-    <t>Tầng Repository &amp; Logic Auth</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cần tối ưu thuật toán sinh ID tự động và hiểu rõ luồng kiểm tra trùng lặp email khi đăng ký từ file </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>customers.csv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Giải thích code CustomerRepository cho tôi, phần tự động sinh ID và hàm login</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI giải thích chi tiết cơ chế Java Stream API để lấy ID lớn nhất. Đồng thời, AI phân tích việc đặt logic </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>check banned</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ở Repo là vi phạm nguyên tắc SRP của MVC.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Em ghi nhận lỗi thiết kế (Technical Debt) này. Em tạm giữ ở Repo để đảm bảo tiến độ test I/O Tuần 3, nhưng đã note lại kịch bản để tự bảo vệ và giải thích lỗi thiết kế kiến trúc này trước giảng viên.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">File </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>CustomerRepository.java</t>
-    </r>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Chức năng Admin (Ban/Unban)</t>
-  </si>
-  <si>
-    <t>Xây dựng chức năng khóa/mở khóa tài khoản khách hàng ở giao diện Admin sao cho tối ưu, tránh lặp code.</t>
-  </si>
-  <si>
-    <t>Giải thích code phần AdminCustomerView và cách xử lý thay đổi trạng thái user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI gợi ý luồng xử lý trạng thái user thành 2 hàm riêng biệt là </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ban()</t>
+      <t xml:space="preserve">Gạch bỏ code của AI. Tự code lại luồng đọc file truyền thống bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BufferedReader</t>
     </r>
     <r>
       <rPr>
@@ -1891,54 +2825,167 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>unban()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Critical Thinking:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Em chủ động bác bỏ gợi ý viết 2 hàm riêng lẻ. Em tự áp dụng tư duy Clean Code để gộp chung thành 1 hàm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>setCustomerStatus(String status)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, giúp tái sử dụng code và dễ bảo trì hơn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">File </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>AdminCustomerView.java</t>
-    </r>
+      <t>FileReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chuẩn Java 8.</t>
+    </r>
+  </si>
+  <si>
+    <t>Có - tách logic khỏi Repo để chuẩn MVC</t>
+  </si>
+  <si>
+    <t>Có - AI phát hiện Repo vi phạm SRP</t>
+  </si>
+  <si>
+    <t>Có - CustomerController.java</t>
+  </si>
+  <si>
+    <t>Có - gộp hàm Ban/Unban để tránh lặp code</t>
+  </si>
+  <si>
+    <t>Có - AI đề xuất 2 hàm riêng cồng kềnh</t>
+  </si>
+  <si>
+    <t>Có - code dự án</t>
+  </si>
+  <si>
+    <t>Có - chặn lỗi crash app do dòng CSV rỗng</t>
+  </si>
+  <si>
+    <t>Có - AI tự tin split() là đủ, bỏ sót edge case</t>
+  </si>
+  <si>
+    <t>Có - CsvRepository.java</t>
+  </si>
+  <si>
+    <t>Có - chặn Admin tự khóa tài khoản (Self-lockout)</t>
+  </si>
+  <si>
+    <t>Có - AI quên kịch bản tự khóa bản thân</t>
+  </si>
+  <si>
+    <t>Có - logic if kiểm tra ID</t>
+  </si>
+  <si>
+    <t>Có - phát hiện AI dùng code sai phiên bản Java 8</t>
+  </si>
+  <si>
+    <t>Có - AI xúi dùng hàm Files.readString() của Java 11</t>
+  </si>
+  <si>
+    <t>Có - tài liệu Java 8 API</t>
+  </si>
+  <si>
+    <t>Các prompt đều quyết định cấu trúc MVC, bảo mật Admin, và xử lý đa luồng FileLock.</t>
+  </si>
+  <si>
+    <t>Chắc chắn, ví dụ việc gộp hàm Admin hay tách logic ra khỏi Repo đã làm thay đổi hẳn luồng MVC.</t>
+  </si>
+  <si>
+    <t>Đã chuẩn bị sẵn sàng luận điểm phản biện trong phần Oral Vivas (Q&amp;A).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">100% các entry đều có đính kèm tên file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc code snippet tương ứng.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đã bác bỏ nhiều đề xuất sai của AI (sai bản Java 8, ảo giác CSV, ảo giác vòng lặp).</t>
+  </si>
+  <si>
+    <r>
+      <t>20 entries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Phủ kín toàn bộ các tuần làm việc).</t>
+    </r>
+  </si>
+  <si>
+    <t>Đã phủ kín: Thiết kế (Use case), Code (MVC/Regex), và Test (JUnit/Debug).</t>
+  </si>
+  <si>
+    <r>
+      <t>5 cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Vượt mức yêu cầu tối thiểu là 3 cases cho Project).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Tất cả đều phân tách rõ Critical Thinking, Contextualization...).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (20/20 entries đều có Evidence cụ thể).</t>
+    </r>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>ddd</t>
   </si>
 </sst>
 </file>
@@ -1961,41 +3008,48 @@
       <sz val="16"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2003,26 +3057,31 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2038,7 +3097,7 @@
       <name val="Arial Unicode MS"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2069,7 +3128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2092,22 +3151,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2156,26 +3204,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2193,10 +3245,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2498,11 +3546,11 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
@@ -2511,10 +3559,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2522,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.8" customHeight="1">
@@ -2530,7 +3578,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.2" customHeight="1">
@@ -2538,7 +3586,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
@@ -2551,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2559,7 +3607,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2568,7 +3616,7 @@
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>9.166666666666666E-2</v>
+        <v>0.18571428571428572</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>9</v>
@@ -2578,74 +3626,74 @@
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
+      <c r="C13" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2653,62 +3701,62 @@
     </row>
     <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2728,187 +3776,191 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="38.5546875" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="29.88671875" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:13" ht="30" customHeight="1">
+      <c r="A2" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:13" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="100.05" customHeight="1">
+      <c r="A4" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>123</v>
+      <c r="F4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>129</v>
+      <c r="A5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="100.05" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>135</v>
+      <c r="A6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="117.6" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="G7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="H7" s="19" t="s">
         <v>138</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="79.95" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="H8" s="19" t="s">
         <v>144</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>149</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -2920,26 +3972,26 @@
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>150</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>155</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -2951,26 +4003,26 @@
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="H10" s="19" t="s">
         <v>157</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>161</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -2978,230 +4030,360 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="1:13" s="19" customFormat="1" ht="126.6" customHeight="1">
+    <row r="11" spans="1:13" ht="126.6" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
+        <v>164</v>
+      </c>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+    </row>
+    <row r="12" spans="1:13" ht="79.95" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" spans="1:13" s="19" customFormat="1" ht="127.8" customHeight="1">
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="19" customFormat="1" ht="148.80000000000001" customHeight="1">
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="19" customFormat="1" ht="181.8" customHeight="1">
+      <c r="A15" s="23">
+        <v>12</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="E15" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="F15" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="G15" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="G12" s="20" t="s">
+    </row>
+    <row r="16" spans="1:13" s="19" customFormat="1" ht="129.6" customHeight="1">
+      <c r="A16" s="7">
+        <v>13</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="19" customFormat="1" ht="151.80000000000001" customHeight="1">
-      <c r="A13" s="23">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="D16" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="E16" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="F16" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="G16" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="H16" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="19" customFormat="1" ht="163.19999999999999" customHeight="1">
+      <c r="A17" s="7">
+        <v>14</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="E17" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="F17" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="G17" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="H17" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="G14" s="20" t="s">
+    </row>
+    <row r="18" spans="1:8" s="19" customFormat="1" ht="146.4" customHeight="1">
+      <c r="A18" s="7">
+        <v>15</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="79.95" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="E18" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="F18" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="G18" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="H18" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G15" s="20" t="s">
+    </row>
+    <row r="19" spans="1:8" s="19" customFormat="1" ht="151.80000000000001" customHeight="1">
+      <c r="A19" s="7">
+        <v>16</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" s="19" customFormat="1" ht="79.95" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="19" t="s">
+      <c r="E19" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="F19" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="G19" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="H19" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F16" s="19" t="s">
+    </row>
+    <row r="20" spans="1:8" s="19" customFormat="1" ht="150" customHeight="1">
+      <c r="A20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="E20" s="19" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="F20" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="19" customFormat="1" ht="144" customHeight="1">
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="19" customFormat="1" ht="144" customHeight="1">
+      <c r="A22" s="7">
+        <v>19</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="19" customFormat="1" ht="195.6" customHeight="1">
+      <c r="A23" s="7">
+        <v>20</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="79.95" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="C24" s="7" t="s">
+        <v>293</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -3248,128 +4430,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="A1" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="A2" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="35.4" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" ht="92.4" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A4" s="7">
+        <v>5</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="19" customFormat="1" ht="105.6" customHeight="1">
       <c r="A5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
       <c r="A6" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
       <c r="A7" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A8" s="7">
+        <v>12</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A9" s="7">
+        <v>16</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="7"/>
@@ -3493,73 +4711,73 @@
     </row>
     <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="7" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3573,251 +4791,317 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="2" max="2" width="51.6640625" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
+    <col min="4" max="4" width="79.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+        <v>96</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="A2" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.8" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4">
+        <v>104</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.4" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="13"/>
+        <v>106</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D8" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D9" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D10" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D15" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="13"/>
+        <v>292</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="A28" s="9">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="A29" s="9">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>270</v>
+      </c>
+      <c r="C29" t="s">
+        <v>271</v>
+      </c>
+      <c r="D29" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="A30" s="9">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>273</v>
+      </c>
+      <c r="C30" t="s">
+        <v>274</v>
+      </c>
+      <c r="D30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="25">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="25">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" t="s">
+        <v>281</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ai_logs/AI.Log.AnhKiet.xlsx
+++ b/ai_logs/AI.Log.AnhKiet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d347304e5a006203/文档/GitHub/Group-2/ai_logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E990FD8B-096B-4DDF-97C2-A8056726A089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -3214,20 +3214,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3543,7 +3543,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="27"/>
@@ -3784,7 +3784,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="27"/>
@@ -3796,7 +3796,7 @@
       <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="27"/>
@@ -4430,7 +4430,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="27"/>
@@ -4440,7 +4440,7 @@
       <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="27"/>
@@ -4801,7 +4801,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="27"/>
@@ -4809,7 +4809,7 @@
       <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="31" t="s">
         <v>97</v>
       </c>
       <c r="B2" s="27"/>
